--- a/Dataset for Data Analytics Project 1.xlsx
+++ b/Dataset for Data Analytics Project 1.xlsx
@@ -12947,7 +12947,44 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -12966,6 +13003,31 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:N1201" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:N1201"/>
+  <tableColumns count="14">
+    <tableColumn id="1" name="OrderID"/>
+    <tableColumn id="2" name="Date" dataDxfId="3"/>
+    <tableColumn id="3" name="CustomerID"/>
+    <tableColumn id="4" name="Product"/>
+    <tableColumn id="5" name="Quantity"/>
+    <tableColumn id="6" name="UnitPrice" dataDxfId="2"/>
+    <tableColumn id="7" name="ShippingAddress"/>
+    <tableColumn id="8" name="PaymentMethod"/>
+    <tableColumn id="9" name="OrderStatus"/>
+    <tableColumn id="10" name="TrackingNumber"/>
+    <tableColumn id="11" name="ItemsInCart"/>
+    <tableColumn id="12" name="CouponCode"/>
+    <tableColumn id="13" name="ReferralSource"/>
+    <tableColumn id="14" name="TotalPrice" dataDxfId="1">
+      <calculatedColumnFormula>PRODUCT(E2,F2)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -13260,16 +13322,18 @@
   <cols>
     <col min="1" max="1" width="11.44140625" customWidth="1"/>
     <col min="2" max="2" width="13.6640625" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" customWidth="1"/>
+    <col min="3" max="3" width="12.77734375" customWidth="1"/>
+    <col min="4" max="4" width="9.5546875" customWidth="1"/>
+    <col min="5" max="5" width="10.21875" customWidth="1"/>
     <col min="6" max="6" width="10.88671875" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.6640625" customWidth="1"/>
-    <col min="8" max="8" width="15.5546875" customWidth="1"/>
+    <col min="7" max="7" width="16.88671875" customWidth="1"/>
+    <col min="8" max="8" width="17.21875" customWidth="1"/>
     <col min="9" max="9" width="16" customWidth="1"/>
-    <col min="10" max="10" width="15.33203125" customWidth="1"/>
+    <col min="10" max="10" width="16.88671875" customWidth="1"/>
     <col min="11" max="11" width="12.6640625" customWidth="1"/>
     <col min="12" max="12" width="14.109375" customWidth="1"/>
-    <col min="13" max="13" width="14.44140625" customWidth="1"/>
-    <col min="14" max="14" width="11.109375" customWidth="1"/>
+    <col min="13" max="13" width="15.21875" customWidth="1"/>
+    <col min="14" max="14" width="11.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -66391,11 +66455,14 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:N1201">
-    <cfRule type="containsBlanks" dxfId="0" priority="1">
+    <cfRule type="containsBlanks" dxfId="4" priority="1">
       <formula>LEN(TRIM(A1))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>